--- a/salon_forms/008_salon_chemical_release_form--salon_forms.xlsx
+++ b/salon_forms/008_salon_chemical_release_form--salon_forms.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -430,10 +440,10 @@
   <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>salon_chemical_release_form</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chemical_reform</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please answer all questions honestly.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -533,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chemical_reform_chemistry</t>
+          <t>salon_information</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chemical_chemistry</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Salon Information</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide your salon information.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -556,38 +574,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>chemical_reform_chemicals</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>chemical_chemicals</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide your name.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>chemical_reform_services</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>chemical_services</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Role in the Salon</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please select your role in the salon.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -602,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>chemical_reform_chemistry_chemicals</t>
+          <t>chemical_information</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chemical_chemistry_chemicals</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Chemical Information</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide chemical information.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -625,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>chemical_reform_sign_off</t>
+          <t>chemical_name</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sign_off</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Chemical Name</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide the name of the chemical being used.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -648,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>chemical_reform_signature</t>
+          <t>concentration</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Concentration</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide the concentration of the chemical being used.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -671,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>chemical_reform_form_date</t>
+          <t>date_of_release</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>form_date</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Date of Release</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide the date of the chemical release.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -689,23 +731,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>chemical_reform_signature_date</t>
+          <t>exposure_duration</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>signature_date</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Exposure Duration</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide how long you have been exposed to the chemical.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -717,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_reform</t>
+          <t>previous_incidents</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>chemical_reform</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Previous Chemical Exposure Incidents</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Have you had any previous chemical exposure incidents?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -740,18 +790,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>chemical_reform_chemistry_chemistry</t>
+          <t>occupation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>chemistry_chemistry</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Occupation</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide your occupation.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -763,18 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_services</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>chemical_services</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Contact Information</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide your contact information.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -786,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_chemistry_chemicals</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>chemical_chemistry_chemicals</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Medical Conditions or Allergies</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please list any medical conditions or allergies that may be affected by chemical exposure.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -809,41 +871,49 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_chemicals_chemistry</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>chemical_chemistry_chemicals_chemistry</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Emergency Contact Information</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please provide the emergency contact person's information.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_sign_off</t>
+          <t>last_release_date</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>chemical_sign_off</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Last Chemical Release Date</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please provide the date of your last chemical release.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -855,38 +925,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_signature</t>
+          <t>release_frequency</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>chemical_signature</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Chemical Release Frequency</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please provide the chemical release frequency.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_form_date</t>
+          <t>safety_procedures</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>chemical_form_date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Chemical Safety Procedures</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Have you received training on chemical safety procedures?</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>yes</t>
@@ -896,23 +974,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_signature_date</t>
+          <t>spill_response</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>chemical_signature_date</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Chemical Spill Response Plan</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Is there a chemical spill response plan?</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -924,15 +1006,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_chemical_chemistry</t>
+          <t>spill_response_location</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>chemical_chemistry</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Chemical Spill Response Plan Location</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Please provide the location of the chemical spill response plan.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -947,18 +1033,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_chemicals_chemistry</t>
+          <t>safety_officer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>chemical_chemistry</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Chemical Safety Officer</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Please provide the chemical safety officer's information.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -970,18 +1060,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_chemical_services</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>chemical_services</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Chemical Inventory</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Please provide the chemical inventory.</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -993,18 +1087,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_chemical_chemicals</t>
+          <t>inventory_storage</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>chemical_chemicals</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Chemical Inventory Storage</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Please describe how you will store the chemical inventory.</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1016,18 +1114,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_chemical_chemistry_chemicals</t>
+          <t>labeling_and_locking</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>chemical_chemistry_chemicals</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Chemical Labeling and Locking</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Are the chemicals labeled and locked?</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1039,18 +1141,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_chemical_services_chemistry</t>
+          <t>access</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>chemical_services_chemistry</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Chemical Access</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Who has access to the chemicals?</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1062,18 +1168,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>chemical_reform_chemical_chemical_signature</t>
+          <t>chemical_usage</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>chemical_signature</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Chemical Usage</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Are the chemicals used properly?</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1083,6 +1193,93 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>role_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>owner/manager</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Owner/Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>role_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>staff_member</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Staff Member</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>role_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
